--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T09:05:22+00:00</t>
+    <t>2024-04-25T09:06:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T09:06:15+00:00</t>
+    <t>2024-05-16T08:04:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-16T08:04:49+00:00</t>
+    <t>2024-05-23T12:00:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.1</t>
+    <t>3.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:00:22+00:00</t>
+    <t>2024-06-05T13:15:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T13:15:20+00:00</t>
+    <t>2024-06-05T13:17:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T13:17:40+00:00</t>
+    <t>2024-06-17T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-17T15:07:22+00:00</t>
+    <t>2024-07-01T14:59:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T13:41:42+00:00</t>
+    <t>2025-02-27T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T09:48:09+00:00</t>
+    <t>2025-03-04T08:17:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T08:17:54+00:00</t>
+    <t>2025-03-06T14:47:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:47:34+00:00</t>
+    <t>2025-03-07T13:06:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T13:06:03+00:00</t>
+    <t>2025-04-23T14:15:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1417,15 +1417,15 @@
   <dimension ref="A1:AN113"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="54.99609375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.0078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.41796875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="25.25" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.15234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.44140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.07421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="21.6484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1436,26 +1436,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="168.19140625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="49.01171875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="35.88671875" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.98046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="144.1953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="42.01953125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="30.76953125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.98828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="28.1484375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="44.65625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="42.9765625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="38.28515625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T14:15:06+00:00</t>
+    <t>2025-05-21T14:32:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:16+00:00</t>
+    <t>2025-07-21T12:31:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-21T12:31:31+00:00</t>
+    <t>2025-10-13T07:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T07:29:09+00:00</t>
+    <t>2025-10-13T07:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T07:29:03+00:00</t>
+    <t>2026-01-29T14:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -880,7 +880,7 @@
 MeasurementResultsTests</t>
   </si>
   <si>
-    <t xml:space="preserve">Observation {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-bmi|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-bodyheight|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-body-temperature|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-body-weight|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-bp|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-heartrate|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-glucose|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-head-circumference|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-pain-severity|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-steps-by-day|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-waist-circumference|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-oxygen-sat}
+    <t xml:space="preserve">Observation {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-bmi|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-bodyheight|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-body-temperature|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-body-weight|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-bp|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-heartrate|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-head-circumference|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-pain-severity|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-steps-by-day|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-waist-circumference|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-oxygen-sat}
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T14:02:34+00:00</t>
+    <t>2026-01-30T09:35:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T09:35:57+00:00</t>
+    <t>2026-01-30T10:15:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.1</t>
+    <t>3.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:15:26+00:00</t>
+    <t>2026-02-02T08:09:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T08:09:27+00:00</t>
+    <t>2026-02-02T08:10:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T08:10:43+00:00</t>
+    <t>2026-02-02T09:29:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0-ballot</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:29:40+00:00</t>
+    <t>2026-02-18T12:52:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T12:52:41+00:00</t>
+    <t>2026-02-23T17:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:17:29+00:00</t>
+    <t>2026-03-18T17:41:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T17:41:07+00:00</t>
+    <t>2026-03-31T09:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:00:47+00:00</t>
+    <t>2026-05-06T11:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T11:42:59+00:00</t>
+    <t>2026-05-07T07:18:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T07:18:48+00:00</t>
+    <t>2026-05-07T07:24:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T07:24:38+00:00</t>
+    <t>2026-06-09T08:46:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/main/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T08:46:34+00:00</t>
+    <t>2026-06-26T10:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
